--- a/data/trans_orig/IP18_E_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP18_E_R-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>106557</t>
+          <t>106433</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>113377</t>
+          <t>113395</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>113866</t>
+          <t>113703</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>123270</t>
+          <t>123098</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>223274</t>
+          <t>224070</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>235037</t>
+          <t>234635</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,03%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1452</t>
+          <t>1434</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8272</t>
+          <t>8396</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3707</t>
+          <t>3879</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13111</t>
+          <t>13274</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6768</t>
+          <t>7170</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>18531</t>
+          <t>17735</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>146140</t>
+          <t>145827</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>155505</t>
+          <t>155377</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>159248</t>
+          <t>159625</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>170106</t>
+          <t>170010</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>309495</t>
+          <t>308166</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>322519</t>
+          <t>322818</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,47%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5389</t>
+          <t>5517</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14754</t>
+          <t>15067</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7129</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17987</t>
+          <t>17610</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>15609</t>
+          <t>15310</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>28633</t>
+          <t>29962</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,86%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>105529</t>
+          <t>105341</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>115068</t>
+          <t>114879</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>115203</t>
+          <t>115423</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>125303</t>
+          <t>125240</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>223997</t>
+          <t>223650</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>238120</t>
+          <t>237402</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>93,84%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6635</t>
+          <t>6824</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16174</t>
+          <t>16362</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5990</t>
+          <t>6053</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16090</t>
+          <t>15870</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>14875</t>
+          <t>15593</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>28998</t>
+          <t>29345</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,6%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>172400</t>
+          <t>170825</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>183596</t>
+          <t>183161</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>157876</t>
+          <t>157842</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>169725</t>
+          <t>169368</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>333944</t>
+          <t>333096</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>349738</t>
+          <t>350533</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,9%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7960</t>
+          <t>8395</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19156</t>
+          <t>20731</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8097</t>
+          <t>8454</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19946</t>
+          <t>19980</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>19640</t>
+          <t>18845</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>35434</t>
+          <t>36282</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,82%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>541227</t>
+          <t>541509</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>559988</t>
+          <t>559492</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>559770</t>
+          <t>559408</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>579694</t>
+          <t>579792</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1106523</t>
+          <t>1106063</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1134395</t>
+          <t>1134911</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,39%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28993</t>
+          <t>29489</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>47754</t>
+          <t>47472</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>33632</t>
+          <t>33534</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>53556</t>
+          <t>53918</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>67912</t>
+          <t>67396</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>95784</t>
+          <t>96244</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,0%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>116492</t>
+          <t>115573</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>126384</t>
+          <t>126143</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>140151</t>
+          <t>140375</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>145630</t>
+          <t>145632</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>260187</t>
+          <t>259495</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>271073</t>
+          <t>271134</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,84%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4481</t>
+          <t>4722</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14373</t>
+          <t>15292</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>629</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6110</t>
+          <t>5886</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6053</t>
+          <t>5992</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16939</t>
+          <t>17631</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>184654</t>
+          <t>184640</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>191306</t>
+          <t>191301</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>187169</t>
+          <t>187430</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>199033</t>
+          <t>198934</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>375401</t>
+          <t>375462</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>388515</t>
+          <t>389425</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,45%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1341</t>
+          <t>1346</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7993</t>
+          <t>8007</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7920</t>
+          <t>8019</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>19784</t>
+          <t>19523</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>11085</t>
+          <t>10175</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>24199</t>
+          <t>24138</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>127076</t>
+          <t>127191</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>137011</t>
+          <t>136905</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>139001</t>
+          <t>138534</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>149085</t>
+          <t>149472</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>269765</t>
+          <t>269757</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>283893</t>
+          <t>283884</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5589</t>
+          <t>5695</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15524</t>
+          <t>15409</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7047</t>
+          <t>6660</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17131</t>
+          <t>17598</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>14839</t>
+          <t>14848</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>28967</t>
+          <t>28975</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>179420</t>
+          <t>180824</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>191959</t>
+          <t>192521</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>183445</t>
+          <t>183431</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>194752</t>
+          <t>194891</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>368414</t>
+          <t>367497</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>384146</t>
+          <t>384280</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,51%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7943</t>
+          <t>7381</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20482</t>
+          <t>19078</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7702</t>
+          <t>7563</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19009</t>
+          <t>19023</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>18210</t>
+          <t>18076</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>33942</t>
+          <t>34859</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,66%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>620381</t>
+          <t>619523</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>639591</t>
+          <t>640023</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>662339</t>
+          <t>661538</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>682374</t>
+          <t>682051</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1290435</t>
+          <t>1291657</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1318748</t>
+          <t>1317988</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,66%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>26423</t>
+          <t>25991</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>45633</t>
+          <t>46491</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>29426</t>
+          <t>29749</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>49461</t>
+          <t>50262</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>59066</t>
+          <t>59826</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>87379</t>
+          <t>86157</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,25%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>109567</t>
+          <t>109029</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>118586</t>
+          <t>118264</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>122090</t>
+          <t>122895</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>130364</t>
+          <t>130330</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>234731</t>
+          <t>235129</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>247059</t>
+          <t>247145</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,64%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4097</t>
+          <t>4419</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13116</t>
+          <t>13654</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2703</t>
+          <t>2737</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10977</t>
+          <t>10172</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8690</t>
+          <t>8604</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21018</t>
+          <t>20620</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,06%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>177523</t>
+          <t>177545</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>186991</t>
+          <t>187555</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>194369</t>
+          <t>194084</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>203307</t>
+          <t>203751</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>374329</t>
+          <t>374344</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>388293</t>
+          <t>388564</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,57%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6882</t>
+          <t>6318</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16350</t>
+          <t>16328</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5167</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14105</t>
+          <t>14390</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>14054</t>
+          <t>13783</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>28018</t>
+          <t>28003</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>125135</t>
+          <t>125771</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>133620</t>
+          <t>133605</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>135050</t>
+          <t>134498</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>142720</t>
+          <t>142767</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>263063</t>
+          <t>262622</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>274209</t>
+          <t>274098</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,66%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3990</t>
+          <t>4005</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12475</t>
+          <t>11839</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3225</t>
+          <t>3178</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10895</t>
+          <t>11447</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9346</t>
+          <t>9457</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>20492</t>
+          <t>20933</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,38%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>173577</t>
+          <t>174276</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>184640</t>
+          <t>185073</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>155779</t>
+          <t>156381</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>169043</t>
+          <t>168758</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>334084</t>
+          <t>334900</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>351794</t>
+          <t>351546</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,94%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8008</t>
+          <t>7575</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19071</t>
+          <t>18372</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12531</t>
+          <t>12816</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25795</t>
+          <t>25193</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>22428</t>
+          <t>22676</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>40138</t>
+          <t>39322</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,51%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>597946</t>
+          <t>597539</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>616934</t>
+          <t>616918</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,7 +6014,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>619551</t>
+          <t>619529</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>638985</t>
+          <t>638715</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1223471</t>
+          <t>1222887</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1251004</t>
+          <t>1251511</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,11%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29880</t>
+          <t>29896</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>48868</t>
+          <t>49275</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30075</t>
+          <t>30345</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>49509</t>
+          <t>49531</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>64869</t>
+          <t>64362</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>92402</t>
+          <t>92986</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,07%</t>
         </is>
       </c>
     </row>
@@ -6574,7 +6574,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13309</t>
+          <t>13470</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -6589,7 +6589,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>78,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -6609,7 +6609,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19251</t>
+          <t>19219</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -6624,7 +6624,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34337</t>
+          <t>34185</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38217</t>
+          <t>38222</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,71%</t>
         </is>
       </c>
     </row>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>3584</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6727,7 +6727,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2415</t>
+          <t>2447</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>498</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>4535</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,71%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22671</t>
+          <t>23241</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27997</t>
+          <t>28014</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>43825</t>
+          <t>44108</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49155</t>
+          <t>49163</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>69550</t>
+          <t>69520</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>76375</t>
+          <t>76089</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,67%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>961</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6304</t>
+          <t>5734</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>573</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5911</t>
+          <t>5628</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2336</t>
+          <t>2622</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9161</t>
+          <t>9191</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,68%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11333</t>
+          <t>12554</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23246</t>
+          <t>23006</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>47,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24958</t>
+          <t>24216</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31680</t>
+          <t>30999</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>38002</t>
+          <t>38776</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52977</t>
+          <t>52923</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>66,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,38%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>3230</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14903</t>
+          <t>13682</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>52,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>681</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6722</t>
+          <t>7464</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4940</t>
+          <t>4994</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>19915</t>
+          <t>19141</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>33,05%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19306</t>
+          <t>19003</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26073</t>
+          <t>25519</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>67,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21844</t>
+          <t>22384</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27682</t>
+          <t>27868</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>43535</t>
+          <t>44453</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>52157</t>
+          <t>52329</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,52%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1976</t>
+          <t>2530</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8743</t>
+          <t>9046</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>828</t>
+          <t>642</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6666</t>
+          <t>6126</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4402</t>
+          <t>4230</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13024</t>
+          <t>12106</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>21,4%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>74582</t>
+          <t>73912</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>89702</t>
+          <t>89845</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>73,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>117908</t>
+          <t>117893</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>127257</t>
+          <t>127020</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>195974</t>
+          <t>196061</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>215015</t>
+          <t>215028</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10612</t>
+          <t>10469</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25732</t>
+          <t>26402</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4335</t>
+          <t>4572</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13684</t>
+          <t>13699</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>16891</t>
+          <t>16878</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>35932</t>
+          <t>35845</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8149,7 +8149,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,46%</t>
         </is>
       </c>
     </row>
